--- a/public/downloads/WangAchieving2021.xlsx
+++ b/public/downloads/WangAchieving2021.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>NH3</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>H</t>
+    <t>NH3</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>132</v>
       </c>
       <c r="N3" s="5">
-        <v>298.4451189041138</v>
+        <v>298445.1189041138</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03239742932089815</v>
+        <v>32.39742932089815</v>
       </c>
       <c r="P3" s="5">
         <v>9212</v>
@@ -709,10 +732,10 @@
         <v>132</v>
       </c>
       <c r="N4" s="5">
-        <v>544.7273769378662</v>
+        <v>544727.3769378662</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04723206251087022</v>
+        <v>47.23206251087022</v>
       </c>
       <c r="P4" s="5">
         <v>11533</v>
@@ -759,10 +782,10 @@
         <v>132</v>
       </c>
       <c r="N5" s="5">
-        <v>1256.90341925621</v>
+        <v>1256903.41925621</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1477840587014944</v>
+        <v>147.7840587014944</v>
       </c>
       <c r="P5" s="5">
         <v>8505</v>
@@ -809,10 +832,10 @@
         <v>132</v>
       </c>
       <c r="N6" s="5">
-        <v>930.4599888324738</v>
+        <v>930459.9888324738</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08441843484235835</v>
+        <v>84.41843484235835</v>
       </c>
       <c r="P6" s="5">
         <v>11022</v>
@@ -859,10 +882,10 @@
         <v>132</v>
       </c>
       <c r="N7" s="5">
-        <v>1231.484601259232</v>
+        <v>1231484.601259232</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1642636522954824</v>
+        <v>164.2636522954824</v>
       </c>
       <c r="P7" s="5">
         <v>7497</v>
@@ -909,10 +932,10 @@
         <v>132</v>
       </c>
       <c r="N8" s="5">
-        <v>109.1140410900116</v>
+        <v>109114.0410900116</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01315895333936464</v>
+        <v>13.15895333936464</v>
       </c>
       <c r="P8" s="5">
         <v>8292</v>
@@ -959,10 +982,10 @@
         <v>132</v>
       </c>
       <c r="N9" s="5">
-        <v>406.334037065506</v>
+        <v>406334.037065506</v>
       </c>
       <c r="O9" s="4">
-        <v>0.0299855388580552</v>
+        <v>29.9855388580552</v>
       </c>
       <c r="P9" s="5">
         <v>13551</v>
@@ -1009,10 +1032,10 @@
         <v>132</v>
       </c>
       <c r="N10" s="5">
-        <v>892.493307352066</v>
+        <v>892493.307352066</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08296089490166073</v>
+        <v>82.96089490166072</v>
       </c>
       <c r="P10" s="5">
         <v>10758</v>
@@ -1059,10 +1082,10 @@
         <v>132</v>
       </c>
       <c r="N11" s="5">
-        <v>851.3482458591461</v>
+        <v>851348.2458591461</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04012765110572898</v>
+        <v>40.12765110572898</v>
       </c>
       <c r="P11" s="5">
         <v>21216</v>
@@ -1109,10 +1132,10 @@
         <v>132</v>
       </c>
       <c r="N12" s="5">
-        <v>164.4830555915833</v>
+        <v>164483.0555915833</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01812685205990558</v>
+        <v>18.12685205990558</v>
       </c>
       <c r="P12" s="5">
         <v>9074</v>
@@ -1159,10 +1182,10 @@
         <v>132</v>
       </c>
       <c r="N13" s="5">
-        <v>655.8055970668793</v>
+        <v>655805.5970668793</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07623873483688436</v>
+        <v>76.23873483688436</v>
       </c>
       <c r="P13" s="5">
         <v>8602</v>
@@ -1209,10 +1232,10 @@
         <v>132</v>
       </c>
       <c r="N14" s="5">
-        <v>2374.028408288956</v>
+        <v>2374028.408288956</v>
       </c>
       <c r="O14" s="4">
-        <v>0.233434455092326</v>
+        <v>233.434455092326</v>
       </c>
       <c r="P14" s="5">
         <v>10170</v>
@@ -1259,10 +1282,10 @@
         <v>132</v>
       </c>
       <c r="N15" s="5">
-        <v>1987.840605735779</v>
+        <v>1987840.605735779</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2293574023001937</v>
+        <v>229.3574023001937</v>
       </c>
       <c r="P15" s="5">
         <v>8667</v>
@@ -1309,10 +1332,10 @@
         <v>132</v>
       </c>
       <c r="N16" s="5">
-        <v>988.0580966472626</v>
+        <v>988058.0966472626</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1033749839555621</v>
+        <v>103.3749839555621</v>
       </c>
       <c r="P16" s="5">
         <v>9558</v>
@@ -1359,10 +1382,10 @@
         <v>132</v>
       </c>
       <c r="N17" s="5">
-        <v>898.4904654026031</v>
+        <v>898490.4654026031</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1027668380879107</v>
+        <v>102.7668380879107</v>
       </c>
       <c r="P17" s="5">
         <v>8743</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.449755900041985</v>
+        <v>0.3825609238438059</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1898566460307242</v>
+        <v>0.3914092827419333</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3333908605264137</v>
+        <v>0.4006863884145538</v>
       </c>
       <c r="E3" s="4">
-        <v>76.25000000000026</v>
+        <v>89.91883116883069</v>
       </c>
       <c r="F3" s="4">
-        <v>84.12395769778306</v>
+        <v>93.2695241000612</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.339870254159675</v>
+      </c>
+      <c r="O3" s="5">
+        <v>43</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2175249667996281</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2146313207860381</v>
+      </c>
+      <c r="R3" s="5">
+        <v>43</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6963071915682355</v>
+        <v>0.472404483816884</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5568972223591814</v>
+        <v>0.4531534301767534</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7412909401923939</v>
+        <v>0.4519318990604411</v>
       </c>
       <c r="E4" s="4">
-        <v>77.75432900432929</v>
+        <v>90.461502782932</v>
       </c>
       <c r="F4" s="4">
-        <v>84.76942241204087</v>
+        <v>93.57306284319704</v>
       </c>
       <c r="G4" s="5">
         <v>44</v>
       </c>
       <c r="H4" s="5">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.115116110071832</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4680233108073971</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4459932505839799</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4307831573981206</v>
+        <v>0.5070600414524358</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3235716984319048</v>
+        <v>0.5182936222868818</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4057483401464068</v>
+        <v>0.4811445532710252</v>
       </c>
       <c r="E5" s="4">
-        <v>77.41651205936923</v>
+        <v>87.92903525046437</v>
       </c>
       <c r="F5" s="4">
-        <v>84.52333740085508</v>
+        <v>90.46522269676636</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5139179207231731</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2699691204606422</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2637373793947401</v>
+      </c>
+      <c r="R5" s="5">
+        <v>43</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,25 +1797,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4450158192375966</v>
+        <v>0.67225486044514</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4524840944760422</v>
+        <v>0.6691675443017187</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4304181050429179</v>
+        <v>0.6267989278279525</v>
       </c>
       <c r="E3" s="4">
-        <v>85.33395176252377</v>
+        <v>81.83209647495346</v>
       </c>
       <c r="F3" s="4">
-        <v>86.8695342688647</v>
+        <v>86.83343502135507</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
@@ -1700,105 +1842,159 @@
         <v>39</v>
       </c>
       <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.495732147793602</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4777977392349235</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.443658231191329</v>
+      </c>
+      <c r="R3" s="5">
+        <v>39</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.9015085641102897</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6797014457556405</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.063893607173999</v>
+      </c>
+      <c r="E4" s="4">
+        <v>80.83951762523191</v>
+      </c>
+      <c r="F4" s="4">
+        <v>84.24420378279441</v>
+      </c>
+      <c r="G4" s="5">
+        <v>44</v>
+      </c>
+      <c r="H4" s="5">
+        <v>33</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6871020026254965</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6987045265329449</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6691950031057455</v>
-      </c>
-      <c r="E4" s="4">
-        <v>87.99551638837355</v>
-      </c>
-      <c r="F4" s="4">
-        <v>92.04723408582466</v>
-      </c>
-      <c r="G4" s="5">
-        <v>44</v>
-      </c>
-      <c r="H4" s="5">
-        <v>43</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1280104844594866</v>
+      </c>
+      <c r="O4" s="5">
+        <v>36</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8972741312126428</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6546600072770377</v>
+      </c>
+      <c r="R4" s="5">
+        <v>33</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7880777044136432</v>
+        <v>0.5340195122387906</v>
       </c>
       <c r="C5" s="4">
-        <v>0.750912731437782</v>
+        <v>0.4898174306468076</v>
       </c>
       <c r="D5" s="4">
-        <v>0.748231110730227</v>
+        <v>0.4827434627735453</v>
       </c>
       <c r="E5" s="4">
-        <v>87.62832405689532</v>
+        <v>78.32560296846037</v>
       </c>
       <c r="F5" s="4">
-        <v>89.46512100874359</v>
+        <v>80.79647142566681</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3526027607224344</v>
+      </c>
+      <c r="O5" s="5">
+        <v>34</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4151834843902705</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3705567953603636</v>
+      </c>
+      <c r="R5" s="5">
+        <v>34</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2826157425115525</v>
+        <v>0.4307831573981206</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2875246419510425</v>
+        <v>0.3235716984319048</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2576008713972855</v>
+        <v>0.4057483401464068</v>
       </c>
       <c r="E3" s="4">
-        <v>85.72742733457039</v>
+        <v>77.41651205936923</v>
       </c>
       <c r="F3" s="4">
-        <v>90.65690461663662</v>
+        <v>84.52333740085508</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.04345846535066986</v>
+      </c>
+      <c r="O3" s="5">
+        <v>38</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4359341399138245</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3249614186763336</v>
+      </c>
+      <c r="R3" s="5">
+        <v>38</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6210616887983633</v>
+        <v>0.6963071915682355</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5942226691324668</v>
+        <v>0.5568972223591814</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5982847120030783</v>
+        <v>0.7412909401923939</v>
       </c>
       <c r="E4" s="4">
-        <v>87.23948670377271</v>
+        <v>77.75432900432929</v>
       </c>
       <c r="F4" s="4">
-        <v>91.64048200122029</v>
+        <v>84.76942241204087</v>
       </c>
       <c r="G4" s="5">
         <v>44</v>
       </c>
       <c r="H4" s="5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1931946180444262</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6441295664440294</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5168173004305666</v>
+      </c>
+      <c r="R4" s="5">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4223343319942863</v>
+        <v>0.449755900041985</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4217177182304007</v>
+        <v>0.1898566460307242</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4334674721126662</v>
+        <v>0.3333908605264137</v>
       </c>
       <c r="E5" s="4">
-        <v>87.93599257885006</v>
+        <v>76.25000000000026</v>
       </c>
       <c r="F5" s="4">
-        <v>92.1199410209481</v>
+        <v>84.12395769778306</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.01264002953414689</v>
+      </c>
+      <c r="O5" s="5">
+        <v>38</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4470973430480997</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1881088463045567</v>
+      </c>
+      <c r="R5" s="5">
+        <v>38</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2397,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5643466648557065</v>
+        <v>0.7880777044136432</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5643466648557065</v>
+        <v>0.750912731437782</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5401591433546855</v>
+        <v>0.748231110730227</v>
       </c>
       <c r="E3" s="4">
-        <v>89.08472479901053</v>
+        <v>87.62832405689532</v>
       </c>
       <c r="F3" s="4">
-        <v>92.18425869432573</v>
+        <v>89.46512100874359</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.7606412773037889</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4114668163374478</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4087694678688554</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.414722591934895</v>
+        <v>0.6871020026254965</v>
       </c>
       <c r="C4" s="4">
-        <v>0.414722591934895</v>
+        <v>0.6987045265329449</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4131359972730438</v>
+        <v>0.6691950031057455</v>
       </c>
       <c r="E4" s="4">
-        <v>90.57282003710573</v>
+        <v>87.99551638837355</v>
       </c>
       <c r="F4" s="4">
-        <v>93.69508846857836</v>
+        <v>92.04723408582466</v>
       </c>
       <c r="G4" s="5">
         <v>44</v>
       </c>
       <c r="H4" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4076121772753161</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5716597621066118</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.579851414651647</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5767777653868094</v>
+        <v>0.4450158192375966</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5767777653868094</v>
+        <v>0.4524840944760422</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5801766606504812</v>
+        <v>0.4304181050429179</v>
       </c>
       <c r="E5" s="4">
-        <v>91.34972170686456</v>
+        <v>85.33395176252377</v>
       </c>
       <c r="F5" s="4">
-        <v>94.26784624771201</v>
+        <v>86.8695342688647</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3158397517759929</v>
+      </c>
+      <c r="O5" s="5">
+        <v>39</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4329487816614648</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4612076623119077</v>
+      </c>
+      <c r="R5" s="5">
+        <v>39</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.171256180035784</v>
+        <v>0.4223343319942863</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2885722261246543</v>
+        <v>0.4217177182304007</v>
       </c>
       <c r="D3" s="4">
-        <v>1.321394887095046</v>
+        <v>0.4334674721126662</v>
       </c>
       <c r="E3" s="4">
-        <v>87.5649350649354</v>
+        <v>87.93599257885006</v>
       </c>
       <c r="F3" s="4">
-        <v>91.73784828147262</v>
+        <v>92.1199410209481</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3175287950593778</v>
+      </c>
+      <c r="O3" s="5">
+        <v>43</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3190428563832287</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3234085058623273</v>
+      </c>
+      <c r="R3" s="5">
+        <v>43</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6210616887983633</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5942226691324668</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5982847120030783</v>
+      </c>
+      <c r="E4" s="4">
+        <v>87.23948670377271</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.64048200122029</v>
+      </c>
+      <c r="G4" s="5">
+        <v>44</v>
+      </c>
+      <c r="H4" s="5">
+        <v>42</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
         <v>2</v>
       </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.708518939712533</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4288634176092633</v>
-      </c>
-      <c r="D4" s="4">
-        <v>3.593938635070862</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.50943104514532</v>
-      </c>
-      <c r="F4" s="4">
-        <v>89.19768151311759</v>
-      </c>
-      <c r="G4" s="5">
-        <v>44</v>
-      </c>
-      <c r="H4" s="5">
-        <v>28</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>16</v>
-      </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.5220139958979589</v>
+      </c>
+      <c r="O4" s="5">
+        <v>42</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4064782086650005</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3694209280403725</v>
+      </c>
+      <c r="R4" s="5">
+        <v>42</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6633806792765905</v>
+        <v>0.2826157425115525</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3869242236212519</v>
+        <v>0.2875246419510425</v>
       </c>
       <c r="D5" s="4">
-        <v>1.161290644962061</v>
+        <v>0.2576008713972855</v>
       </c>
       <c r="E5" s="4">
-        <v>89.05612244897944</v>
+        <v>85.72742733457039</v>
       </c>
       <c r="F5" s="4">
-        <v>91.31482611348389</v>
+        <v>90.65690461663662</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2259665786635217</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2482192765289715</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2470732214418079</v>
+      </c>
+      <c r="R5" s="5">
+        <v>43</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2997,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6402574406360599</v>
+        <v>0.5767777653868094</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6402574406360599</v>
+        <v>0.5767777653868094</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6211381897664953</v>
+        <v>0.5801766606504812</v>
       </c>
       <c r="E3" s="4">
-        <v>86.9480519480519</v>
+        <v>91.34972170686456</v>
       </c>
       <c r="F3" s="4">
-        <v>91.52837095790137</v>
+        <v>94.26784624771201</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
@@ -2566,37 +3056,55 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5767777653868094</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2300094804259286</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2300094804259286</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9207922486662441</v>
+        <v>0.414722591934895</v>
       </c>
       <c r="C4" s="4">
-        <v>0.887307618707784</v>
+        <v>0.414722591934895</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9036730801083382</v>
+        <v>0.4131359972730438</v>
       </c>
       <c r="E4" s="4">
-        <v>88.75000000000003</v>
+        <v>90.57282003710573</v>
       </c>
       <c r="F4" s="4">
-        <v>92.98733984136683</v>
+        <v>93.69508846857836</v>
       </c>
       <c r="G4" s="5">
         <v>44</v>
       </c>
       <c r="H4" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2605,27 +3113,45 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2635448207848557</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3616152306072644</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3616152306072644</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6375624496957496</v>
+        <v>0.5643466648557065</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6375624496957496</v>
+        <v>0.5643466648557065</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6525089263526502</v>
+        <v>0.5401591433546855</v>
       </c>
       <c r="E5" s="4">
-        <v>89.99999999999994</v>
+        <v>89.08472479901053</v>
       </c>
       <c r="F5" s="4">
-        <v>93.57941834451897</v>
+        <v>92.18425869432573</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5639654242831139</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.175968995534066</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.175968995534066</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.309954867717789</v>
+        <v>0.6633806792765905</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3249598096569551</v>
+        <v>0.3869242236212519</v>
       </c>
       <c r="D3" s="4">
-        <v>1.362472147964609</v>
+        <v>1.161290644962061</v>
       </c>
       <c r="E3" s="4">
-        <v>89.577149041434</v>
+        <v>89.05612244897944</v>
       </c>
       <c r="F3" s="4">
-        <v>93.37807606263989</v>
+        <v>91.31482611348389</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>5</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.5254842787772173</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7453396905429347</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6670835395172909</v>
+      </c>
+      <c r="R3" s="5">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.211487112861833</v>
+        <v>1.708518939712533</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5981121360722036</v>
+        <v>0.4288634176092633</v>
       </c>
       <c r="D4" s="4">
-        <v>1.503735088133411</v>
+        <v>3.593938635070862</v>
       </c>
       <c r="E4" s="4">
-        <v>88.88064316635756</v>
+        <v>85.50943104514532</v>
       </c>
       <c r="F4" s="4">
-        <v>92.27832011389057</v>
+        <v>89.19768151311759</v>
       </c>
       <c r="G4" s="5">
         <v>44</v>
       </c>
       <c r="H4" s="5">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>16</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>5</v>
+      </c>
+      <c r="M4" s="5">
+        <v>8</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.038945099946431</v>
+      </c>
+      <c r="O4" s="5">
         <v>36</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="P4" s="4">
+        <v>1.793798360443279</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.005286269431963</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
         <v>8</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6392004933073978</v>
+        <v>1.171256180035784</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4810694402161374</v>
+        <v>0.2885722261246543</v>
       </c>
       <c r="D5" s="4">
-        <v>0.687283664857458</v>
+        <v>1.321394887095046</v>
       </c>
       <c r="E5" s="4">
-        <v>89.83998144712359</v>
+        <v>87.5649350649354</v>
       </c>
       <c r="F5" s="4">
-        <v>92.81218222493396</v>
+        <v>91.73784828147262</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.193212952796876</v>
+      </c>
+      <c r="O5" s="5">
+        <v>41</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.242655417804757</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9527970991539403</v>
+      </c>
+      <c r="R5" s="5">
+        <v>33</v>
+      </c>
+      <c r="S5" s="5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3597,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3612238178697654</v>
+        <v>0.6375624496957496</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3612238178697654</v>
+        <v>0.6375624496957496</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3684971645303683</v>
+        <v>0.6525089263526502</v>
       </c>
       <c r="E3" s="4">
-        <v>86.59013605442173</v>
+        <v>89.99999999999994</v>
       </c>
       <c r="F3" s="4">
-        <v>90.76723611958556</v>
+        <v>93.57941834451897</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
@@ -2992,25 +3656,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6361447163214016</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2342803898596937</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2342803898596937</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7872070516618386</v>
+        <v>0.9207922486662441</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7543955761786993</v>
+        <v>0.887307618707784</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7606422320929017</v>
+        <v>0.9036730801083382</v>
       </c>
       <c r="E4" s="4">
-        <v>88.61781076066789</v>
+        <v>88.75000000000003</v>
       </c>
       <c r="F4" s="4">
-        <v>92.81650396583295</v>
+        <v>92.98733984136683</v>
       </c>
       <c r="G4" s="5">
         <v>44</v>
@@ -3033,25 +3715,43 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.9040889907906107</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3241747514515406</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3241747514515406</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4839126596201592</v>
+        <v>0.6402574406360599</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4839126596201592</v>
+        <v>0.6402574406360599</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4936714165394966</v>
+        <v>0.6211381897664953</v>
       </c>
       <c r="E5" s="4">
-        <v>89.79437229437229</v>
+        <v>86.9480519480519</v>
       </c>
       <c r="F5" s="4">
-        <v>93.48764490543009</v>
+        <v>91.52837095790137</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.6402574406360599</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2483167485066411</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2483167485066411</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6392004933073978</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4810694402161374</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.687283664857458</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.83998144712359</v>
+      </c>
+      <c r="F3" s="4">
+        <v>92.81218222493396</v>
+      </c>
+      <c r="G3" s="5">
+        <v>44</v>
+      </c>
+      <c r="H3" s="5">
+        <v>39</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.4694117567542536</v>
+      </c>
+      <c r="O3" s="5">
+        <v>41</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7043995105571305</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6226422783617804</v>
+      </c>
+      <c r="R3" s="5">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.211487112861833</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5981121360722036</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.503735088133411</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.88064316635756</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.27832011389057</v>
+      </c>
+      <c r="G4" s="5">
+        <v>44</v>
+      </c>
+      <c r="H4" s="5">
+        <v>36</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6975581519778593</v>
+      </c>
+      <c r="O4" s="5">
+        <v>40</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.198135092623625</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6480037148914394</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.309954867717789</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3249598096569551</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.362472147964609</v>
+      </c>
+      <c r="E5" s="4">
+        <v>89.577149041434</v>
+      </c>
+      <c r="F5" s="4">
+        <v>93.37807606263989</v>
+      </c>
+      <c r="G5" s="5">
+        <v>44</v>
+      </c>
+      <c r="H5" s="5">
+        <v>31</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>13</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.308502289607945</v>
+      </c>
+      <c r="O5" s="5">
+        <v>42</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.436779433240563</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.042174370551808</v>
+      </c>
+      <c r="R5" s="5">
+        <v>36</v>
+      </c>
+      <c r="S5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4839126596201592</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4839126596201592</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4936714165394966</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.79437229437229</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.48764490543009</v>
+      </c>
+      <c r="G3" s="5">
+        <v>44</v>
+      </c>
+      <c r="H3" s="5">
+        <v>44</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4308135330287519</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2329876031709475</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2329876031709475</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7872070516618386</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7543955761786993</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7606422320929017</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.61781076066789</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.81650396583295</v>
+      </c>
+      <c r="G4" s="5">
+        <v>44</v>
+      </c>
+      <c r="H4" s="5">
+        <v>43</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.7866247762272404</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3199010915892007</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3199010915892007</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3612238178697654</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3612238178697654</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3684971645303683</v>
+      </c>
+      <c r="E5" s="4">
+        <v>86.59013605442173</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.76723611958556</v>
+      </c>
+      <c r="G5" s="5">
+        <v>44</v>
+      </c>
+      <c r="H5" s="5">
+        <v>44</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.149651149391998</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3142062716026707</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3142062716026707</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>99.24242424242425</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3251163841133216</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3270991979516501</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3367289893183896</v>
+      </c>
+      <c r="K3" s="4">
+        <v>87.78731189445463</v>
+      </c>
+      <c r="L3" s="4">
+        <v>91.77674394956331</v>
+      </c>
+      <c r="M3" s="5">
+        <v>132</v>
+      </c>
+      <c r="N3" s="5">
+        <v>298445.1189041138</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.39742932089815</v>
+      </c>
+      <c r="P3" s="5">
+        <v>9212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>93.93939393939394</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.460577349248199</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.4308470853889716</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4854937314626478</v>
+      </c>
+      <c r="K4" s="4">
+        <v>86.02195423623994</v>
+      </c>
+      <c r="L4" s="4">
+        <v>88.58001152464375</v>
+      </c>
+      <c r="M4" s="5">
+        <v>132</v>
+      </c>
+      <c r="N4" s="5">
+        <v>544727.3769378662</v>
+      </c>
+      <c r="O4" s="4">
+        <v>47.23206251087022</v>
+      </c>
+      <c r="P4" s="5">
+        <v>11533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>96.96969696969697</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2985887186728337</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2925121801424904</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2888451840139389</v>
+      </c>
+      <c r="K5" s="4">
+        <v>87.80225726654321</v>
+      </c>
+      <c r="L5" s="4">
+        <v>91.74081418209015</v>
+      </c>
+      <c r="M5" s="5">
+        <v>132</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1256903.41925621</v>
+      </c>
+      <c r="O5" s="4">
+        <v>147.7840587014944</v>
+      </c>
+      <c r="P5" s="5">
+        <v>8505</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>94.6969696969697</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4448655711830229</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3982344395597086</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.4564670214709931</v>
+      </c>
+      <c r="K6" s="4">
+        <v>86.07915893630181</v>
+      </c>
+      <c r="L6" s="4">
+        <v>89.02184597654545</v>
+      </c>
+      <c r="M6" s="5">
+        <v>132</v>
+      </c>
+      <c r="N6" s="5">
+        <v>930459.9888324738</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.41843484235835</v>
+      </c>
+      <c r="P6" s="5">
+        <v>11022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2208476629000735</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2208476629000735</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2220428679719947</v>
+      </c>
+      <c r="K7" s="4">
+        <v>91.55534941249222</v>
+      </c>
+      <c r="L7" s="4">
+        <v>94.53799742390341</v>
+      </c>
+      <c r="M7" s="5">
+        <v>132</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1231484.601259232</v>
+      </c>
+      <c r="O7" s="4">
+        <v>164.2636522954824</v>
+      </c>
+      <c r="P7" s="5">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>97.72727272727273</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3185057993558891</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3081206502549193</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.3243202991654532</v>
+      </c>
+      <c r="K8" s="4">
+        <v>89.4364564007418</v>
+      </c>
+      <c r="L8" s="4">
+        <v>92.43593654667434</v>
+      </c>
+      <c r="M8" s="5">
+        <v>132</v>
+      </c>
+      <c r="N8" s="5">
+        <v>109114.0410900116</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13.15895333936464</v>
+      </c>
+      <c r="P8" s="5">
+        <v>8292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>80.3030303030303</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="D9" s="3">
+        <v>10.60606060606061</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5967517849459456</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.4858998330080795</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.6325048768013513</v>
+      </c>
+      <c r="K9" s="4">
+        <v>80.33240568954844</v>
+      </c>
+      <c r="L9" s="4">
+        <v>83.95803674327142</v>
+      </c>
+      <c r="M9" s="5">
+        <v>132</v>
+      </c>
+      <c r="N9" s="5">
+        <v>406334.037065506</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.9855388580552</v>
+      </c>
+      <c r="P9" s="5">
+        <v>13551</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>86.36363636363636</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12.87878787878788</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.509053683135318</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3432958551371524</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.4807965809164515</v>
+      </c>
+      <c r="K10" s="4">
+        <v>77.14028035456631</v>
+      </c>
+      <c r="L10" s="4">
+        <v>84.47223917022683</v>
+      </c>
+      <c r="M10" s="5">
+        <v>132</v>
+      </c>
+      <c r="N10" s="5">
+        <v>892493.307352066</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.96089490166072</v>
+      </c>
+      <c r="P10" s="5">
+        <v>10758</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>93.93939393939394</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.4720251200351748</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.4845889299248156</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.4790005721958898</v>
+      </c>
+      <c r="K11" s="4">
+        <v>86.98593073593099</v>
+      </c>
+      <c r="L11" s="4">
+        <v>89.46062978781238</v>
+      </c>
+      <c r="M11" s="5">
+        <v>132</v>
+      </c>
+      <c r="N11" s="5">
+        <v>851348.2458591461</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.12765110572898</v>
+      </c>
+      <c r="P11" s="5">
+        <v>21216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>96.96969696969697</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.3245801138590669</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.3128624472794801</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.327667893566681</v>
+      </c>
+      <c r="K12" s="4">
+        <v>86.96763553906437</v>
+      </c>
+      <c r="L12" s="4">
+        <v>91.47244254626827</v>
+      </c>
+      <c r="M12" s="5">
+        <v>132</v>
+      </c>
+      <c r="N12" s="5">
+        <v>164483.0555915833</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.12685205990558</v>
+      </c>
+      <c r="P12" s="5">
+        <v>9074</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.255864568855753</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.255864568855753</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2686424825973637</v>
+      </c>
+      <c r="K13" s="4">
+        <v>90.33575551432692</v>
+      </c>
+      <c r="L13" s="4">
+        <v>93.38239780353872</v>
+      </c>
+      <c r="M13" s="5">
+        <v>132</v>
+      </c>
+      <c r="N13" s="5">
+        <v>655805.5970668793</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.23873483688436</v>
+      </c>
+      <c r="P13" s="5">
+        <v>8602</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>74.24242424242425</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="D14" s="3">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.303030303030303</v>
+      </c>
+      <c r="F14" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="G14" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.260597822930323</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.8599225589623954</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2.100501738037728</v>
+      </c>
+      <c r="K14" s="4">
+        <v>87.37682951968651</v>
+      </c>
+      <c r="L14" s="4">
+        <v>90.75011863602634</v>
+      </c>
+      <c r="M14" s="5">
+        <v>132</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2374028.408288956</v>
+      </c>
+      <c r="O14" s="4">
+        <v>233.434455092326</v>
+      </c>
+      <c r="P14" s="5">
+        <v>10170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2689239632726251</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2689239632726251</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2727896069083162</v>
+      </c>
+      <c r="K15" s="4">
+        <v>88.56601731601731</v>
+      </c>
+      <c r="L15" s="4">
+        <v>92.69837638126225</v>
+      </c>
+      <c r="M15" s="5">
+        <v>132</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1987840.605735779</v>
+      </c>
+      <c r="O15" s="4">
+        <v>229.3574023001937</v>
+      </c>
+      <c r="P15" s="5">
+        <v>8667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="D16" s="3">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="G16" s="3">
+        <v>9.848484848484848</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.113104678807106</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.7677826798240478</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.268488524720627</v>
+      </c>
+      <c r="K16" s="4">
+        <v>89.43259121830555</v>
+      </c>
+      <c r="L16" s="4">
+        <v>92.82285946715555</v>
+      </c>
+      <c r="M16" s="5">
+        <v>132</v>
+      </c>
+      <c r="N16" s="5">
+        <v>988058.0966472626</v>
+      </c>
+      <c r="O16" s="4">
+        <v>103.3749839555621</v>
+      </c>
+      <c r="P16" s="5">
+        <v>9558</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.289031655454273</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.289031655454273</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2990156631625455</v>
+      </c>
+      <c r="K17" s="4">
+        <v>88.33410636982065</v>
+      </c>
+      <c r="L17" s="4">
+        <v>92.35712833028315</v>
+      </c>
+      <c r="M17" s="5">
+        <v>132</v>
+      </c>
+      <c r="N17" s="5">
+        <v>898490.4654026031</v>
+      </c>
+      <c r="O17" s="4">
+        <v>102.7668380879107</v>
+      </c>
+      <c r="P17" s="5">
+        <v>8743</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3517,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3558,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
         <v>1</v>
@@ -3693,13 +5869,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>131</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>124</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>3</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>128</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>125</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>132</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>129</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>106</v>
+      </c>
+      <c r="C9" s="5">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>11</v>
+      </c>
+      <c r="G9" s="5">
+        <v>3</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>114</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>18</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>17</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>15</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>124</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>3</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>128</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>132</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>98</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>33</v>
+      </c>
+      <c r="E14" s="5">
+        <v>7</v>
+      </c>
+      <c r="F14" s="5">
+        <v>8</v>
+      </c>
+      <c r="G14" s="5">
+        <v>18</v>
+      </c>
+      <c r="H14" s="5">
+        <v>7</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>5</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>8</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>132</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>110</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>8</v>
+      </c>
+      <c r="G16" s="5">
+        <v>13</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>8</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>132</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,25 +6864,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2838929629549305</v>
+        <v>0.46029752295627</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2838929629549305</v>
+        <v>0.46029752295627</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2732952702668131</v>
+        <v>0.4633689072688867</v>
       </c>
       <c r="E3" s="4">
-        <v>87.76051329622754</v>
+        <v>88.32405689548543</v>
       </c>
       <c r="F3" s="4">
-        <v>91.58480780964018</v>
+        <v>92.61160260321321</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
@@ -3960,10 +6923,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.447262290893956</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2834758712577556</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2834758712577556</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4479051126525684</v>
@@ -4001,25 +6982,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1996382178419248</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4544986045181334</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4635481587791995</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.46029752295627</v>
+        <v>0.2838929629549305</v>
       </c>
       <c r="C5" s="4">
-        <v>0.46029752295627</v>
+        <v>0.2838929629549305</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4633689072688867</v>
+        <v>0.2732952702668131</v>
       </c>
       <c r="E5" s="4">
-        <v>88.32405689548543</v>
+        <v>87.76051329622754</v>
       </c>
       <c r="F5" s="4">
-        <v>92.61160260321321</v>
+        <v>91.58480780964018</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1197977329545459</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2373746765640758</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2373746765640758</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,34 +7164,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3190411123961729</v>
+        <v>0.6422041009344949</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2882091093091558</v>
+        <v>0.621270570316971</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3350694603141164</v>
+        <v>0.5934961277211683</v>
       </c>
       <c r="E3" s="4">
-        <v>84.99226963512675</v>
+        <v>86.96196660482373</v>
       </c>
       <c r="F3" s="4">
-        <v>87.84141753101514</v>
+        <v>88.46196868008838</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -4173,10 +7223,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5328689189386417</v>
+      </c>
+      <c r="O3" s="5">
+        <v>41</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3766943039649163</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3753236359304945</v>
+      </c>
+      <c r="R3" s="5">
+        <v>41</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.7465562480607663</v>
@@ -4214,34 +7282,52 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3279256473885783</v>
+      </c>
+      <c r="O4" s="5">
+        <v>42</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6877143909780886</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6348646763941956</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6422041009344949</v>
+        <v>0.3190411123961729</v>
       </c>
       <c r="C5" s="4">
-        <v>0.621270570316971</v>
+        <v>0.2882091093091558</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5934961277211683</v>
+        <v>0.3350694603141164</v>
       </c>
       <c r="E5" s="4">
-        <v>86.96196660482373</v>
+        <v>84.99226963512675</v>
       </c>
       <c r="F5" s="4">
-        <v>88.46196868008838</v>
+        <v>87.84141753101514</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>1</v>
@@ -4255,9 +7341,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.01094169295140004</v>
+      </c>
+      <c r="O5" s="5">
+        <v>42</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3173233528015921</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2858885186409568</v>
+      </c>
+      <c r="R5" s="5">
+        <v>42</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,34 +7464,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.309662366459551</v>
+        <v>0.3272320310084483</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3086945844853438</v>
+        <v>0.3183657288134868</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2836404576744165</v>
+        <v>0.325467135846173</v>
       </c>
       <c r="E3" s="4">
-        <v>86.92717996289447</v>
+        <v>87.80844155844177</v>
       </c>
       <c r="F3" s="4">
-        <v>90.91061622940835</v>
+        <v>91.55938580435206</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -4386,10 +7523,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2687459225067176</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2419476780480213</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2418176410695499</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4618422338905723</v>
@@ -4427,34 +7582,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2272745142589312</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4376711313648507</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4272229844652515</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3272320310084483</v>
+        <v>0.309662366459551</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3183657288134868</v>
+        <v>0.3086945844853438</v>
       </c>
       <c r="D5" s="4">
-        <v>0.325467135846173</v>
+        <v>0.2836404576744165</v>
       </c>
       <c r="E5" s="4">
-        <v>87.80844155844177</v>
+        <v>86.92717996289447</v>
       </c>
       <c r="F5" s="4">
-        <v>91.55938580435206</v>
+        <v>90.91061622940835</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>1</v>
@@ -4468,9 +7641,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2445764579853519</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2161473466056288</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2073169721235315</v>
+      </c>
+      <c r="R5" s="5">
+        <v>43</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7672,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,34 +7764,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3423071712386445</v>
+        <v>0.5668454376900627</v>
       </c>
       <c r="C3" s="4">
-        <v>0.344932694905202</v>
+        <v>0.5647441767816713</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3398896408775313</v>
+        <v>0.5372716400250449</v>
       </c>
       <c r="E3" s="4">
-        <v>84.29112554112552</v>
+        <v>87.26808905380324</v>
       </c>
       <c r="F3" s="4">
-        <v>86.89165141346339</v>
+        <v>89.6644295302015</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
       </c>
       <c r="H3" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4599,10 +7823,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5000812704823803</v>
+      </c>
+      <c r="O3" s="5">
+        <v>43</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3100364046168708</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3135926376017164</v>
+      </c>
+      <c r="R3" s="5">
+        <v>43</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.7964856983718082</v>
@@ -4640,34 +7882,52 @@
       <c r="M4" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3476986750922447</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7162095014912609</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5733304001408531</v>
+      </c>
+      <c r="R4" s="5">
+        <v>40</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5668454376900627</v>
+        <v>0.3423071712386445</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5647441767816713</v>
+        <v>0.344932694905202</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5372716400250449</v>
+        <v>0.3398896408775313</v>
       </c>
       <c r="E5" s="4">
-        <v>87.26808905380324</v>
+        <v>84.29112554112552</v>
       </c>
       <c r="F5" s="4">
-        <v>89.6644295302015</v>
+        <v>86.89165141346339</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
       </c>
       <c r="H5" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4681,9 +7941,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1842561717681487</v>
+      </c>
+      <c r="O5" s="5">
+        <v>42</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.308350807440937</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3181334648203726</v>
+      </c>
+      <c r="R5" s="5">
+        <v>42</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7972,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7991,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8033,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,25 +8064,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1258835606700317</v>
+        <v>0.3261514302671871</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1258835606700317</v>
+        <v>0.3261514302671871</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1209957839935007</v>
+        <v>0.342178837479878</v>
       </c>
       <c r="E3" s="4">
-        <v>91.16187384044522</v>
+        <v>92.10111317254166</v>
       </c>
       <c r="F3" s="4">
-        <v>94.41656497864544</v>
+        <v>94.87695749440711</v>
       </c>
       <c r="G3" s="5">
         <v>44</v>
@@ -4812,10 +8123,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2437908036752726</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2240045745169452</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2240045745169452</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3990267642776333</v>
@@ -4853,25 +8182,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2716451570330802</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3108590920144871</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3108590920144871</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3261514302671871</v>
+        <v>0.1258835606700317</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3261514302671871</v>
+        <v>0.1258835606700317</v>
       </c>
       <c r="D5" s="4">
-        <v>0.342178837479878</v>
+        <v>0.1209957839935007</v>
       </c>
       <c r="E5" s="4">
-        <v>92.10111317254166</v>
+        <v>91.16187384044522</v>
       </c>
       <c r="F5" s="4">
-        <v>94.87695749440711</v>
+        <v>94.41656497864544</v>
       </c>
       <c r="G5" s="5">
         <v>44</v>
@@ -4894,9 +8241,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.02052590596146977</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1276793221687881</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1276793221687881</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8272,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5070600414524358</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5182936222868818</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4811445532710252</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.92903525046437</v>
-      </c>
-      <c r="F3" s="4">
-        <v>90.46522269676636</v>
-      </c>
-      <c r="G3" s="5">
-        <v>44</v>
-      </c>
-      <c r="H3" s="5">
-        <v>43</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.472404483816884</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4531534301767534</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4519318990604411</v>
-      </c>
-      <c r="E4" s="4">
-        <v>90.461502782932</v>
-      </c>
-      <c r="F4" s="4">
-        <v>93.57306284319704</v>
-      </c>
-      <c r="G4" s="5">
-        <v>44</v>
-      </c>
-      <c r="H4" s="5">
-        <v>43</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3825609238438059</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3914092827419333</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4006863884145538</v>
-      </c>
-      <c r="E5" s="4">
-        <v>89.91883116883069</v>
-      </c>
-      <c r="F5" s="4">
-        <v>93.2695241000612</v>
-      </c>
-      <c r="G5" s="5">
-        <v>44</v>
-      </c>
-      <c r="H5" s="5">
-        <v>43</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5340195122387906</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4898174306468076</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4827434627735453</v>
-      </c>
-      <c r="E3" s="4">
-        <v>78.32560296846037</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.79647142566681</v>
-      </c>
-      <c r="G3" s="5">
-        <v>44</v>
-      </c>
-      <c r="H3" s="5">
-        <v>34</v>
-      </c>
-      <c r="I3" s="5">
-        <v>7</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9015085641102897</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6797014457556405</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.063893607173999</v>
-      </c>
-      <c r="E4" s="4">
-        <v>80.83951762523191</v>
-      </c>
-      <c r="F4" s="4">
-        <v>84.24420378279441</v>
-      </c>
-      <c r="G4" s="5">
-        <v>44</v>
-      </c>
-      <c r="H4" s="5">
-        <v>33</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.67225486044514</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6691675443017187</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6267989278279525</v>
-      </c>
-      <c r="E5" s="4">
-        <v>81.83209647495346</v>
-      </c>
-      <c r="F5" s="4">
-        <v>86.83343502135507</v>
-      </c>
-      <c r="G5" s="5">
-        <v>44</v>
-      </c>
-      <c r="H5" s="5">
-        <v>39</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>4</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>4</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/WangAchieving2021.xlsx
+++ b/public/downloads/WangAchieving2021.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.339870254159675</v>
+        <v>-0.33923741923644</v>
       </c>
       <c r="O3" s="5">
         <v>43</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2175249667996281</v>
+        <v>0.2174962015758448</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2146313207860381</v>
+        <v>0.2146166036948</v>
       </c>
       <c r="R3" s="5">
         <v>43</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.115116110071832</v>
+        <v>-0.09806181951978488</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4680233108073971</v>
+        <v>0.4672381806486305</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4459932505839799</v>
+        <v>0.4455864729924989</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5139179207231731</v>
+        <v>-0.4253819600938584</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2699691204606422</v>
+        <v>0.2635545595321825</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2637373793947401</v>
+        <v>0.2592326184593235</v>
       </c>
       <c r="R5" s="5">
         <v>43</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.495732147793602</v>
+        <v>-0.5766214890754782</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4777977392349235</v>
+        <v>0.4814745274750087</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.443658231191329</v>
+        <v>0.4415841455174347</v>
       </c>
       <c r="R3" s="5">
         <v>39</v>
@@ -1916,16 +1916,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1280104844594866</v>
+        <v>0.210830916010309</v>
       </c>
       <c r="O4" s="5">
         <v>36</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8972741312126428</v>
+        <v>0.8995930214011671</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6546600072770377</v>
+        <v>0.6452033106267636</v>
       </c>
       <c r="R4" s="5">
         <v>33</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3526027607224344</v>
+        <v>-0.346975734566513</v>
       </c>
       <c r="O5" s="5">
         <v>34</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4151834843902705</v>
+        <v>0.4149185752969722</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3705567953603636</v>
+        <v>0.3704832968931656</v>
       </c>
       <c r="R5" s="5">
         <v>34</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04345846535066986</v>
+        <v>-0.02079521730338474</v>
       </c>
       <c r="O3" s="5">
         <v>38</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4359341399138245</v>
+        <v>0.4318317274450351</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3249614186763336</v>
+        <v>0.3225968619279758</v>
       </c>
       <c r="R3" s="5">
         <v>38</v>
@@ -2216,22 +2216,22 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1931946180444262</v>
+        <v>0.486254682094426</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6441295664440294</v>
+        <v>0.5984698173849597</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5168173004305666</v>
+        <v>0.4509502489101595</v>
       </c>
       <c r="R4" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.01264002953414689</v>
+        <v>0.02318239863492266</v>
       </c>
       <c r="O5" s="5">
         <v>38</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4470973430480997</v>
+        <v>0.4459065203726061</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1881088463045567</v>
+        <v>0.18783972205933</v>
       </c>
       <c r="R5" s="5">
         <v>38</v>
@@ -2457,16 +2457,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7606412773037889</v>
+        <v>-0.7327048109145835</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4114668163374478</v>
+        <v>0.4112769720274876</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4087694678688554</v>
+        <v>0.4085705833536589</v>
       </c>
       <c r="R3" s="5">
         <v>42</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4076121772753161</v>
+        <v>-0.5600007991306484</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5716597621066118</v>
+        <v>0.5692571443591574</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.579851414651647</v>
+        <v>0.5738490006343603</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3158397517759929</v>
+        <v>-0.1248203104187269</v>
       </c>
       <c r="O5" s="5">
         <v>39</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4329487816614648</v>
+        <v>0.4103365307015668</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4612076623119077</v>
+        <v>0.429361347207025</v>
       </c>
       <c r="R5" s="5">
         <v>39</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3175287950593778</v>
+        <v>-0.3634952604188584</v>
       </c>
       <c r="O3" s="5">
         <v>43</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3190428563832287</v>
+        <v>0.315085634347435</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3234085058623273</v>
+        <v>0.3204282429735961</v>
       </c>
       <c r="R3" s="5">
         <v>43</v>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5220139958979589</v>
+        <v>-0.5372505881387042</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2259665786635217</v>
+        <v>-0.1377633085503476</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2482192765289715</v>
+        <v>0.2340783635690142</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2470732214418079</v>
+        <v>0.2346546888807626</v>
       </c>
       <c r="R5" s="5">
         <v>43</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5767777653868094</v>
+        <v>-0.6056400695524644</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2300094804259286</v>
+        <v>0.2293438224035278</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2300094804259286</v>
+        <v>0.2293438224035278</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2635448207848557</v>
+        <v>-0.3122467291395878</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3616152306072644</v>
+        <v>0.3610005284618554</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3616152306072644</v>
+        <v>0.3610005284618554</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5639654242831139</v>
+        <v>-0.5573416684856056</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.175968995534066</v>
+        <v>0.1759167596709713</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.175968995534066</v>
+        <v>0.1759167596709713</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -3357,22 +3357,22 @@
         <v>5</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5254842787772173</v>
+        <v>0.05973253390405286</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7453396905429347</v>
+        <v>0.6568196819746637</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6670835395172909</v>
+        <v>0.4380896614519429</v>
       </c>
       <c r="R3" s="5">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="S3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3416,22 +3416,22 @@
         <v>8</v>
       </c>
       <c r="N4" s="4">
-        <v>1.038945099946431</v>
+        <v>0.2294286369724432</v>
       </c>
       <c r="O4" s="5">
         <v>36</v>
       </c>
       <c r="P4" s="4">
-        <v>1.793798360443279</v>
+        <v>1.641249800929062</v>
       </c>
       <c r="Q4" s="4">
-        <v>1.005286269431963</v>
+        <v>0.4886142279970878</v>
       </c>
       <c r="R4" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S4" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -3475,22 +3475,22 @@
         <v>12</v>
       </c>
       <c r="N5" s="4">
-        <v>1.193212952796876</v>
+        <v>0.2937412301253346</v>
       </c>
       <c r="O5" s="5">
         <v>41</v>
       </c>
       <c r="P5" s="4">
-        <v>1.242655417804757</v>
+        <v>0.9682222713477636</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9527970991539403</v>
+        <v>0.1670469673932627</v>
       </c>
       <c r="R5" s="5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S5" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6361447163214016</v>
+        <v>-0.670196812818169</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2342803898596937</v>
+        <v>0.230719954343261</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2342803898596937</v>
+        <v>0.230719954343261</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9040889907906107</v>
+        <v>-0.9128242630540626</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6402574406360599</v>
+        <v>-0.5883611619429132</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2483167485066411</v>
+        <v>0.2403885162374686</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2483167485066411</v>
+        <v>0.2403885162374686</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -3957,22 +3957,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4694117567542536</v>
+        <v>0.02828286105068401</v>
       </c>
       <c r="O3" s="5">
         <v>41</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7043995105571305</v>
+        <v>0.6362014291559979</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6226422783617804</v>
+        <v>0.4798614853569181</v>
       </c>
       <c r="R3" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4016,22 +4016,22 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6975581519778593</v>
+        <v>0.269503581468598</v>
       </c>
       <c r="O4" s="5">
         <v>40</v>
       </c>
       <c r="P4" s="4">
-        <v>1.198135092623625</v>
+        <v>1.13256628380226</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6480037148914394</v>
+        <v>0.5615430297701928</v>
       </c>
       <c r="R4" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S4" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -4075,22 +4075,22 @@
         <v>11</v>
       </c>
       <c r="N5" s="4">
-        <v>1.308502289607945</v>
+        <v>0.2893379656452879</v>
       </c>
       <c r="O5" s="5">
         <v>42</v>
       </c>
       <c r="P5" s="4">
-        <v>1.436779433240563</v>
+        <v>1.109334464961822</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.042174370551808</v>
+        <v>0.2121417604255516</v>
       </c>
       <c r="R5" s="5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="S5" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4308135330287519</v>
+        <v>-0.4643086934083982</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2329876031709475</v>
+        <v>0.2303799628481842</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2329876031709475</v>
+        <v>0.2303799628481842</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -4316,16 +4316,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7866247762272404</v>
+        <v>-0.8446664431685349</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3199010915892007</v>
+        <v>0.3136209575955443</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3199010915892007</v>
+        <v>0.3136209575955443</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.149651149391998</v>
+        <v>0.2123509711163365</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3142062716026707</v>
+        <v>0.3096098717499154</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3142062716026707</v>
+        <v>0.3096098717499154</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3251163841133216</v>
+        <v>0.3177334949445635</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3270991979516501</v>
+        <v>0.3198507170504819</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3367289893183896</v>
+        <v>0.3249430362564895</v>
       </c>
       <c r="K3" s="4">
         <v>87.78731189445463</v>
@@ -4571,13 +4571,13 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="H4" s="4">
-        <v>0.460577349248199</v>
+        <v>0.4575830908850163</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4308470853889716</v>
+        <v>0.4283625105804423</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4854937314626478</v>
+        <v>0.4855826107734284</v>
       </c>
       <c r="K4" s="4">
         <v>86.02195423623994</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2985887186728337</v>
+        <v>0.2976879324681552</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2925121801424904</v>
+        <v>0.2920604053271063</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2888451840139389</v>
+        <v>0.2890829522677285</v>
       </c>
       <c r="K5" s="4">
         <v>87.80225726654321</v>
@@ -4671,13 +4671,13 @@
         <v>2.272727272727273</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4448655711830229</v>
+        <v>0.4403218092133598</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3982344395597086</v>
+        <v>0.3934775589287747</v>
       </c>
       <c r="J6" s="4">
-        <v>0.4564670214709931</v>
+        <v>0.4564360756328714</v>
       </c>
       <c r="K6" s="4">
         <v>86.07915893630181</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2208476629000735</v>
+        <v>0.2184538852045741</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2208476629000735</v>
+        <v>0.2184538852045741</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2220428679719947</v>
+        <v>0.2206664398921324</v>
       </c>
       <c r="K7" s="4">
         <v>91.55534941249222</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3185057993558891</v>
+        <v>0.3160963139188859</v>
       </c>
       <c r="I8" s="4">
-        <v>0.3081206502549193</v>
+        <v>0.3064785650488742</v>
       </c>
       <c r="J8" s="4">
-        <v>0.3243202991654532</v>
+        <v>0.319193186890926</v>
       </c>
       <c r="K8" s="4">
         <v>89.4364564007418</v>
@@ -4821,13 +4821,13 @@
         <v>2.272727272727273</v>
       </c>
       <c r="H9" s="4">
-        <v>0.5967517849459456</v>
+        <v>0.5986620413910494</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4858998330080795</v>
+        <v>0.4821690850965168</v>
       </c>
       <c r="J9" s="4">
-        <v>0.6325048768013513</v>
+        <v>0.6314112033187209</v>
       </c>
       <c r="K9" s="4">
         <v>80.33240568954844</v>
@@ -4853,13 +4853,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>86.36363636363636</v>
+        <v>85.60606060606061</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
       </c>
       <c r="D10" s="3">
-        <v>13.63636363636363</v>
+        <v>14.39393939393939</v>
       </c>
       <c r="E10" s="3">
         <v>0.7575757575757576</v>
@@ -4868,16 +4868,16 @@
         <v>12.87878787878788</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="H10" s="4">
-        <v>0.509053683135318</v>
+        <v>0.4920693550675336</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3432958551371524</v>
+        <v>0.3193075168247215</v>
       </c>
       <c r="J10" s="4">
-        <v>0.4807965809164515</v>
+        <v>0.4688366057881151</v>
       </c>
       <c r="K10" s="4">
         <v>77.14028035456631</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4720251200351748</v>
+        <v>0.4636235490294039</v>
       </c>
       <c r="I11" s="4">
-        <v>0.4845889299248156</v>
+        <v>0.4724239037839124</v>
       </c>
       <c r="J11" s="4">
-        <v>0.4790005721958898</v>
+        <v>0.4643973520629295</v>
       </c>
       <c r="K11" s="4">
         <v>86.98593073593099</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.3245801138590669</v>
+        <v>0.3185474021938166</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3128624472794801</v>
+        <v>0.3076894144330709</v>
       </c>
       <c r="J12" s="4">
-        <v>0.327667893566681</v>
+        <v>0.3219297621378218</v>
       </c>
       <c r="K12" s="4">
         <v>86.96763553906437</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.255864568855753</v>
+        <v>0.2554203701787849</v>
       </c>
       <c r="I13" s="4">
-        <v>0.255864568855753</v>
+        <v>0.2554203701787849</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2686424825973637</v>
+        <v>0.2683119380570574</v>
       </c>
       <c r="K13" s="4">
         <v>90.33575551432692</v>
@@ -5053,13 +5053,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>74.24242424242425</v>
+        <v>71.21212121212122</v>
       </c>
       <c r="C14" s="3">
         <v>0.7575757575757576</v>
       </c>
       <c r="D14" s="3">
-        <v>25</v>
+        <v>28.03030303030303</v>
       </c>
       <c r="E14" s="3">
         <v>5.303030303030303</v>
@@ -5068,16 +5068,16 @@
         <v>6.060606060606061</v>
       </c>
       <c r="G14" s="3">
-        <v>13.63636363636363</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="H14" s="4">
-        <v>1.260597822930323</v>
+        <v>1.08876391808383</v>
       </c>
       <c r="I14" s="4">
-        <v>0.8599225589623954</v>
+        <v>0.3671740402609727</v>
       </c>
       <c r="J14" s="4">
-        <v>2.100501738037728</v>
+        <v>1.93383710536849</v>
       </c>
       <c r="K14" s="4">
         <v>87.37682951968651</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2689239632726251</v>
+        <v>0.2650944073440901</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2689239632726251</v>
+        <v>0.2650944073440901</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2727896069083162</v>
+        <v>0.2685004689642095</v>
       </c>
       <c r="K15" s="4">
         <v>88.56601731601731</v>
@@ -5153,13 +5153,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3">
-        <v>83.33333333333334</v>
+        <v>81.06060606060606</v>
       </c>
       <c r="C16" s="3">
         <v>0.7575757575757576</v>
       </c>
       <c r="D16" s="3">
-        <v>15.90909090909091</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -5168,16 +5168,16 @@
         <v>6.060606060606061</v>
       </c>
       <c r="G16" s="3">
-        <v>9.848484848484848</v>
+        <v>12.12121212121212</v>
       </c>
       <c r="H16" s="4">
-        <v>1.113104678807106</v>
+        <v>0.9593673926400266</v>
       </c>
       <c r="I16" s="4">
-        <v>0.7677826798240478</v>
+        <v>0.4272774143389196</v>
       </c>
       <c r="J16" s="4">
-        <v>1.268488524720627</v>
+        <v>1.095328200847721</v>
       </c>
       <c r="K16" s="4">
         <v>89.43259121830555</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.289031655454273</v>
+        <v>0.2845369307312147</v>
       </c>
       <c r="I17" s="4">
-        <v>0.289031655454273</v>
+        <v>0.2845369307312147</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2990156631625455</v>
+        <v>0.2947501226387365</v>
       </c>
       <c r="K17" s="4">
         <v>88.33410636982065</v>
@@ -6418,13 +6418,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" s="5">
         <v>0</v>
       </c>
       <c r="D10" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" s="5">
         <v>1</v>
@@ -6433,7 +6433,7 @@
         <v>17</v>
       </c>
       <c r="G10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="5">
         <v>1</v>
@@ -6594,13 +6594,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C14" s="5">
         <v>1</v>
       </c>
       <c r="D14" s="5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E14" s="5">
         <v>7</v>
@@ -6609,7 +6609,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H14" s="5">
         <v>7</v>
@@ -6682,13 +6682,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="5">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C16" s="5">
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E16" s="5">
         <v>0</v>
@@ -6697,7 +6697,7 @@
         <v>8</v>
       </c>
       <c r="G16" s="5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H16" s="5">
         <v>0</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.447262290893956</v>
+        <v>-0.4972240450733807</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2834758712577556</v>
+        <v>0.2813546540171294</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2834758712577556</v>
+        <v>0.2813546540171294</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1996382178419248</v>
+        <v>-0.0938930474803783</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4544986045181334</v>
+        <v>0.4414773277246489</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4635481587791995</v>
+        <v>0.4508052330422161</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1197977329545459</v>
+        <v>0.177172228195559</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2373746765640758</v>
+        <v>0.2303685030919124</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2373746765640758</v>
+        <v>0.2303685030919124</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -7224,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5328689189386417</v>
+        <v>-0.5787139689782634</v>
       </c>
       <c r="O3" s="5">
         <v>41</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3766943039649163</v>
+        <v>0.3725265721431325</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3753236359304945</v>
+        <v>0.3742054639783086</v>
       </c>
       <c r="R3" s="5">
         <v>41</v>
@@ -7283,16 +7283,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3279256473885783</v>
+        <v>-0.3573650487960549</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6877143909780886</v>
+        <v>0.6860833336812159</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6348646763941956</v>
+        <v>0.6352683759834645</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -7342,16 +7342,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.01094169295140004</v>
+        <v>0.0802909562808054</v>
       </c>
       <c r="O5" s="5">
         <v>42</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3173233528015921</v>
+        <v>0.3141393668307005</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2858885186409568</v>
+        <v>0.2792505684176701</v>
       </c>
       <c r="R5" s="5">
         <v>42</v>
@@ -7524,13 +7524,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2687459225067176</v>
+        <v>-0.2849415324890288</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2419476780480213</v>
+        <v>0.2412115139579162</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2418176410695499</v>
@@ -7583,16 +7583,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2272745142589312</v>
+        <v>-0.1975258673192002</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4376711313648507</v>
+        <v>0.4357049368409207</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4272229844652515</v>
+        <v>0.425902893485875</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2445764579853519</v>
+        <v>-0.2456397222413216</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
@@ -7651,7 +7651,7 @@
         <v>0.2161473466056288</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2073169721235315</v>
+        <v>0.2072922450478113</v>
       </c>
       <c r="R5" s="5">
         <v>43</v>
@@ -7824,16 +7824,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5000812704823803</v>
+        <v>-0.5883891533012502</v>
       </c>
       <c r="O3" s="5">
         <v>43</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3100364046168708</v>
+        <v>0.2995304756639763</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3135926376017164</v>
+        <v>0.3048960564131469</v>
       </c>
       <c r="R3" s="5">
         <v>43</v>
@@ -7883,16 +7883,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3476986750922447</v>
+        <v>-0.296790923748631</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7162095014912609</v>
+        <v>0.7135085563760103</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5733304001408531</v>
+        <v>0.5678139729468967</v>
       </c>
       <c r="R4" s="5">
         <v>40</v>
@@ -7942,13 +7942,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1842561717681487</v>
+        <v>-0.1935932322667213</v>
       </c>
       <c r="O5" s="5">
         <v>42</v>
       </c>
       <c r="P5" s="4">
-        <v>0.308350807440937</v>
+        <v>0.3079263956000928</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3181334648203726</v>
@@ -8124,16 +8124,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2437908036752726</v>
+        <v>-0.3195152164116735</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2240045745169452</v>
+        <v>0.2186190029292034</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2240045745169452</v>
+        <v>0.2186190029292034</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -8183,16 +8183,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2716451570330802</v>
+        <v>-0.2719662113668164</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3108590920144871</v>
+        <v>0.3108590920144872</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3108590920144871</v>
+        <v>0.3108590920144872</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -8242,16 +8242,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.02052590596146977</v>
+        <v>0.0007914803099993151</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1276793221687881</v>
+        <v>0.1258835606700317</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1276793221687881</v>
+        <v>0.1258835606700317</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
